--- a/1 SENAT/senat_2025_test/data_v1_senate/tables/senate_2025q1_FINAL.xlsx
+++ b/1 SENAT/senat_2025_test/data_v1_senate/tables/senate_2025q1_FINAL.xlsx
@@ -1086,7 +1086,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -4134,7 +4134,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Stock</t>
+          <t>Option</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -41195,7 +41195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41211,20 +41211,25 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>is_senator</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>nous</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>quiver</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>verdict</t>
         </is>
@@ -41241,16 +41246,19 @@
           <t>Richard Blumenthal</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
         <v>92</v>
       </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
       <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
         <v>92</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>quiver_sans_donnee</t>
         </is>
@@ -41267,16 +41275,19 @@
           <t>David H McCormick</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
         <v>73</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>12</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>61</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>nous_plus</t>
         </is>
@@ -41293,16 +41304,19 @@
           <t>Markwayne Mullin</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
         <v>66</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>53</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>13</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>nous_plus</t>
         </is>
@@ -41319,16 +41333,19 @@
           <t>Ashley Moody</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
         <v>44</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>15</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>29</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>nous_plus</t>
         </is>
@@ -41345,16 +41362,19 @@
           <t>John Boozman</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>38</v>
+      <c r="C6" t="b">
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>38</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="inlineStr">
+        <v>38</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>concordant</t>
         </is>
@@ -41371,16 +41391,19 @@
           <t>Shelley M Capito</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" t="b">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
         <v>24</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>22</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>2</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>nous_plus</t>
         </is>
@@ -41397,16 +41420,19 @@
           <t>John Fetterman</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
         <v>9</v>
       </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
       <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
         <v>9</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>quiver_sans_donnee</t>
         </is>
@@ -41423,16 +41449,19 @@
           <t>Rick Scott</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" t="b">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
         <v>6</v>
       </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
       <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
         <v>6</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>quiver_sans_donnee</t>
         </is>
@@ -41449,16 +41478,19 @@
           <t>Thomas H Tuberville</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>6</v>
+      <c r="C10" t="b">
+        <v>1</v>
       </c>
       <c r="D10" t="n">
         <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>concordant</t>
         </is>
@@ -41475,16 +41507,19 @@
           <t>Ron L Wyden</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>4</v>
+      <c r="C11" t="b">
+        <v>1</v>
       </c>
       <c r="D11" t="n">
         <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>concordant</t>
         </is>
@@ -41501,16 +41536,19 @@
           <t>Sheldon Whitehouse</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>3</v>
+      <c r="C12" t="b">
+        <v>1</v>
       </c>
       <c r="D12" t="n">
         <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>concordant</t>
         </is>
@@ -41519,24 +41557,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R000595</t>
+          <t>S001203</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Marco Rubio</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2</v>
+          <t>Tina Smith</t>
+        </is>
+      </c>
+      <c r="C13" t="b">
+        <v>1</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>concordant</t>
         </is>
@@ -41545,24 +41586,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M000355</t>
+          <t>R000595</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A. Mitchell McConnell, Jr.</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>2</v>
+          <t>Marco Rubio</t>
+        </is>
+      </c>
+      <c r="C14" t="b">
+        <v>1</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>concordant</t>
         </is>
@@ -41571,24 +41615,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S001203</t>
+          <t>M000355</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tina Smith</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>2</v>
+          <t>A. Mitchell McConnell, Jr.</t>
+        </is>
+      </c>
+      <c r="C15" t="b">
+        <v>1</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>concordant</t>
         </is>
@@ -41597,24 +41644,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C000174</t>
+          <t>M000934</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Thomas R Carper</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
+          <t>Jerry Moran,</t>
+        </is>
+      </c>
+      <c r="C16" t="b">
         <v>1</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>concordant</t>
         </is>
@@ -41623,24 +41673,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H000601</t>
+          <t>C000174</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>William F Hagerty, IV</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
+          <t>Thomas R Carper</t>
+        </is>
+      </c>
+      <c r="C17" t="b">
         <v>1</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>concordant</t>
         </is>
@@ -41649,24 +41702,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B001299</t>
+          <t>H000601</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>James Banks</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
+          <t>William F Hagerty, IV</t>
+        </is>
+      </c>
+      <c r="C18" t="b">
         <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>concordant</t>
         </is>
@@ -41675,52 +41731,29 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M000934</t>
+          <t>B001299</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jerry Moran,</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
+          <t>James Banks</t>
+        </is>
+      </c>
+      <c r="C19" t="b">
         <v>1</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>concordant</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>N000147</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Eleanor Holmes Norton</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>quiver_seul</t>
         </is>
       </c>
     </row>
